--- a/TestData/TMTC0019612_VerifyExternalContactFeaturesOnSFLightning.xlsx
+++ b/TestData/TMTC0019612_VerifyExternalContactFeaturesOnSFLightning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HL\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D74864-E144-4AB2-BD32-79668912507C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE387A3-7EF4-4B77-ABD0-F8D7904F9651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="53">
   <si>
     <t>Users</t>
   </si>
@@ -190,12 +190,6 @@
   </si>
   <si>
     <t>Business</t>
-  </si>
-  <si>
-    <t>ContactName</t>
-  </si>
-  <si>
-    <t>Test LVContact</t>
   </si>
 </sst>
 </file>
@@ -800,7 +794,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539639EE-7BFC-4886-96EB-3951B3718C01}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -808,10 +802,9 @@
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -827,11 +820,8 @@
       <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -846,9 +836,6 @@
       </c>
       <c r="E2" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
